--- a/payment_forms/006_winter_collection_pre_order_form--payment_forms.xlsx
+++ b/payment_forms/006_winter_collection_pre_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in-store_pickup',_'value':_'store'}</t>
+          <t>in-store_pickup</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In-store pickup', 'value': 'store'}</t>
+          <t>In-store pickup</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'home_delivery',_'value':_'home'}</t>
+          <t>home_delivery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Home delivery', 'value': 'home'}</t>
+          <t>Home delivery</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'check',_'value':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Check', 'value': 'check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New', 'value': 'new'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'shipped',_'value':_'shipped'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Shipped', 'value': 'shipped'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'canceled',_'value':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Canceled', 'value': 'canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
